--- a/test-import-complet.xlsx
+++ b/test-import-complet.xlsx
@@ -6,7 +6,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Test complet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -73,6 +73,18 @@
     <t>Format</t>
   </si>
   <si>
+    <t>logo_path</t>
+  </si>
+  <si>
+    <t>logo_status</t>
+  </si>
+  <si>
+    <t>matched_name</t>
+  </si>
+  <si>
+    <t>match_method</t>
+  </si>
+  <si>
     <t>Prix promo</t>
   </si>
   <si>
@@ -88,6 +100,18 @@
     <t>A4</t>
   </si>
   <si>
+    <t>logos_jpeg/arkopharma.png</t>
+  </si>
+  <si>
+    <t>found</t>
+  </si>
+  <si>
+    <t>Arkopharma</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
     <t>SOIN VISAGE</t>
   </si>
   <si>
@@ -100,6 +124,12 @@
     <t>Vitrine</t>
   </si>
   <si>
+    <t>logos_jpeg/avene.png</t>
+  </si>
+  <si>
+    <t>Avène</t>
+  </si>
+  <si>
     <t>HYGIÈNE BUCCO-DENTAIRE</t>
   </si>
   <si>
@@ -112,6 +142,12 @@
     <t>Rayon</t>
   </si>
   <si>
+    <t>logos_jpeg/laboratoires_pierre_fabre.png</t>
+  </si>
+  <si>
+    <t>Laboratoires Pierre Fabre</t>
+  </si>
+  <si>
     <t>CAPILLAIRE</t>
   </si>
   <si>
@@ -124,6 +160,12 @@
     <t>Petite</t>
   </si>
   <si>
+    <t>logos_jpeg/klorane.png</t>
+  </si>
+  <si>
+    <t>Klorane</t>
+  </si>
+  <si>
     <t>MINCEUR</t>
   </si>
   <si>
@@ -142,6 +184,12 @@
     <t>60 comprimés</t>
   </si>
   <si>
+    <t>logos_jpeg/pileje.png</t>
+  </si>
+  <si>
+    <t>PiLeJe</t>
+  </si>
+  <si>
     <t>DERMO-COSMÉTIQUE</t>
   </si>
   <si>
@@ -151,6 +199,12 @@
     <t>Flacon 30 ml</t>
   </si>
   <si>
+    <t>logos_jpeg/la_roche_posay.png</t>
+  </si>
+  <si>
+    <t>La Roche-Posay</t>
+  </si>
+  <si>
     <t>DIGESTION</t>
   </si>
   <si>
@@ -169,6 +223,12 @@
     <t>30 comprimés</t>
   </si>
   <si>
+    <t>logos_jpeg/nutrisante.vignette.svg</t>
+  </si>
+  <si>
+    <t>Nutrisanté</t>
+  </si>
+  <si>
     <t>Bon</t>
   </si>
   <si>
@@ -181,6 +241,12 @@
     <t>31/12/2026</t>
   </si>
   <si>
+    <t>logos_jpeg/haleon.png</t>
+  </si>
+  <si>
+    <t>Haleon</t>
+  </si>
+  <si>
     <t>BÉBÉ</t>
   </si>
   <si>
@@ -190,6 +256,12 @@
     <t>30/09/2026</t>
   </si>
   <si>
+    <t>logos_jpeg/mustela.png</t>
+  </si>
+  <si>
+    <t>Mustela</t>
+  </si>
+  <si>
     <t>VÉTÉRINAIRE</t>
   </si>
   <si>
@@ -199,12 +271,24 @@
     <t>15/11/2026</t>
   </si>
   <si>
+    <t>logos_jpeg/boehringer_ingelheim.vignette.svg</t>
+  </si>
+  <si>
+    <t>Boehringer Ingelheim</t>
+  </si>
+  <si>
     <t>SEVRAGE TABAGIQUE</t>
   </si>
   <si>
     <t>Patchs NICORETTE 25 mg</t>
   </si>
   <si>
+    <t>logos_jpeg/kenvue.png</t>
+  </si>
+  <si>
+    <t>Kenvue</t>
+  </si>
+  <si>
     <t>Lot</t>
   </si>
   <si>
@@ -214,6 +298,12 @@
     <t>Lot de 3 boîtes</t>
   </si>
   <si>
+    <t>logos_jpeg/sanofi.png</t>
+  </si>
+  <si>
+    <t>Sanofi</t>
+  </si>
+  <si>
     <t>SOLAIRE</t>
   </si>
   <si>
@@ -223,6 +313,12 @@
     <t>Lot de 2 sprays</t>
   </si>
   <si>
+    <t>logos_jpeg/bioderma.png</t>
+  </si>
+  <si>
+    <t>Bioderma</t>
+  </si>
+  <si>
     <t>CORPS</t>
   </si>
   <si>
@@ -232,6 +328,12 @@
     <t>Lot de 4 flacons</t>
   </si>
   <si>
+    <t>logos_jpeg/sanex.png</t>
+  </si>
+  <si>
+    <t>Sanex</t>
+  </si>
+  <si>
     <t>IMMUNITÉ</t>
   </si>
   <si>
@@ -247,21 +349,45 @@
     <t>Spray solaire GARNIER SPF50</t>
   </si>
   <si>
+    <t>logos_jpeg/l_oreal.vignette.svg</t>
+  </si>
+  <si>
+    <t>L'Oréal</t>
+  </si>
+  <si>
     <t>Savon de Marseille LE PETIT MARSEILLAIS</t>
   </si>
   <si>
+    <t>logos_jpeg/le_petit_marseillais.vignette.svg</t>
+  </si>
+  <si>
+    <t>Le Petit Marseillais</t>
+  </si>
+  <si>
     <t>NUTRITION SPORTIVE</t>
   </si>
   <si>
     <t>Barre protéinée EAFIT</t>
   </si>
   <si>
+    <t>logos_jpeg/eafit.jpg</t>
+  </si>
+  <si>
+    <t>Eafit</t>
+  </si>
+  <si>
     <t>YEUX</t>
   </si>
   <si>
     <t>Sérum physiologique dosettes</t>
   </si>
   <si>
+    <t>not_found</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
     <t>2ᵉ produit</t>
   </si>
   <si>
@@ -271,6 +397,12 @@
     <t>Tube 75 ml</t>
   </si>
   <si>
+    <t>logos_jpeg/neutrogena.webp</t>
+  </si>
+  <si>
+    <t>Neutrogena</t>
+  </si>
+  <si>
     <t>Bain de bouche LISTERINE</t>
   </si>
   <si>
@@ -283,10 +415,22 @@
     <t>Pot 15 ml</t>
   </si>
   <si>
+    <t>logos_jpeg/caudalie.png</t>
+  </si>
+  <si>
+    <t>Caudalie</t>
+  </si>
+  <si>
     <t>PIEDS</t>
   </si>
   <si>
     <t>Crème anti-callosités AKILEÏNE</t>
+  </si>
+  <si>
+    <t>logos_jpeg/akileine.jpg</t>
+  </si>
+  <si>
+    <t>Akileine</t>
   </si>
 </sst>
 </file>
@@ -306,18 +450,12 @@
       <color theme="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0E7A4D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -331,36 +469,13 @@
   </borders>
   <cellXfs count="2">
     <xf/>
-    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf fontId="1" applyFont="1"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -420,16 +535,28 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>31.9</v>
@@ -438,21 +565,33 @@
         <v>26.9</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>19.9</v>
@@ -461,21 +600,33 @@
         <v>14.9</v>
       </c>
       <c r="R3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>8.5</v>
@@ -484,21 +635,33 @@
         <v>5.9</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>9.9</v>
@@ -507,21 +670,33 @@
         <v>6.9</v>
       </c>
       <c r="R5" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="T5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" t="s">
+        <v>29</v>
+      </c>
+      <c r="V5" t="s">
+        <v>49</v>
+      </c>
+      <c r="W5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>15.5</v>
@@ -530,21 +705,33 @@
         <v>11.9</v>
       </c>
       <c r="R6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" t="s">
+        <v>28</v>
+      </c>
+      <c r="U6" t="s">
+        <v>29</v>
+      </c>
+      <c r="V6" t="s">
         <v>30</v>
       </c>
-      <c r="S6" t="s">
-        <v>38</v>
+      <c r="W6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D7">
         <v>13.2</v>
@@ -553,21 +740,33 @@
         <v>9.9</v>
       </c>
       <c r="R7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S7" t="s">
         <v>41</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" t="s">
+        <v>29</v>
+      </c>
+      <c r="V7" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>39.9</v>
@@ -576,21 +775,33 @@
         <v>31.9</v>
       </c>
       <c r="R8" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="T8" t="s">
+        <v>61</v>
+      </c>
+      <c r="U8" t="s">
+        <v>29</v>
+      </c>
+      <c r="V8" t="s">
+        <v>62</v>
+      </c>
+      <c r="W8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D9">
         <v>24.9</v>
@@ -599,21 +810,33 @@
         <v>18.9</v>
       </c>
       <c r="R9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="S9" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="T9" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" t="s">
+        <v>29</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>12.9</v>
@@ -622,101 +845,161 @@
         <v>8.9</v>
       </c>
       <c r="R10" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="T10" t="s">
+        <v>69</v>
+      </c>
+      <c r="U10" t="s">
+        <v>29</v>
+      </c>
+      <c r="V10" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="S11" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="T11" t="s">
+        <v>75</v>
+      </c>
+      <c r="U11" t="s">
+        <v>29</v>
+      </c>
+      <c r="V11" t="s">
+        <v>76</v>
+      </c>
+      <c r="W11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F12">
         <v>1.5</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="S12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T12" t="s">
+        <v>80</v>
+      </c>
+      <c r="U12" t="s">
+        <v>29</v>
+      </c>
+      <c r="V12" t="s">
+        <v>81</v>
+      </c>
+      <c r="W12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="S13" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="T13" t="s">
+        <v>85</v>
+      </c>
+      <c r="U13" t="s">
+        <v>29</v>
+      </c>
+      <c r="V13" t="s">
+        <v>86</v>
+      </c>
+      <c r="W13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="S14" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="T14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V14" t="s">
+        <v>90</v>
+      </c>
+      <c r="W14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -728,21 +1011,33 @@
         <v>19.98</v>
       </c>
       <c r="R15" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="S15" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="T15" t="s">
+        <v>94</v>
+      </c>
+      <c r="U15" t="s">
+        <v>29</v>
+      </c>
+      <c r="V15" t="s">
+        <v>95</v>
+      </c>
+      <c r="W15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -754,21 +1049,33 @@
         <v>24.9</v>
       </c>
       <c r="R16" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="T16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U16" t="s">
+        <v>29</v>
+      </c>
+      <c r="V16" t="s">
+        <v>100</v>
+      </c>
+      <c r="W16" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -780,21 +1087,33 @@
         <v>9.8</v>
       </c>
       <c r="R17" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="S17" t="s">
+        <v>41</v>
+      </c>
+      <c r="T17" t="s">
+        <v>104</v>
+      </c>
+      <c r="U17" t="s">
+        <v>29</v>
+      </c>
+      <c r="V17" t="s">
+        <v>105</v>
+      </c>
+      <c r="W17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -806,21 +1125,33 @@
         <v>15.9</v>
       </c>
       <c r="R18" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="T18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U18" t="s">
+        <v>29</v>
+      </c>
+      <c r="V18" t="s">
+        <v>30</v>
+      </c>
+      <c r="W18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -841,18 +1172,30 @@
         <v>29.9</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="T19" t="s">
+        <v>111</v>
+      </c>
+      <c r="U19" t="s">
+        <v>29</v>
+      </c>
+      <c r="V19" t="s">
+        <v>112</v>
+      </c>
+      <c r="W19" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -873,18 +1216,30 @@
         <v>13.5</v>
       </c>
       <c r="S20" t="s">
+        <v>41</v>
+      </c>
+      <c r="T20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U20" t="s">
+        <v>29</v>
+      </c>
+      <c r="V20" t="s">
+        <v>115</v>
+      </c>
+      <c r="W20" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -905,18 +1260,30 @@
         <v>10</v>
       </c>
       <c r="S21" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="T21" t="s">
+        <v>118</v>
+      </c>
+      <c r="U21" t="s">
+        <v>29</v>
+      </c>
+      <c r="V21" t="s">
+        <v>119</v>
+      </c>
+      <c r="W21" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -937,18 +1304,24 @@
         <v>8.9</v>
       </c>
       <c r="S22" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="U22" t="s">
+        <v>122</v>
+      </c>
+      <c r="W22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="D23">
         <v>4.95</v>
@@ -957,21 +1330,33 @@
         <v>50</v>
       </c>
       <c r="R23" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="S23" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="T23" t="s">
+        <v>127</v>
+      </c>
+      <c r="U23" t="s">
+        <v>29</v>
+      </c>
+      <c r="V23" t="s">
+        <v>128</v>
+      </c>
+      <c r="W23" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="D24">
         <v>6.5</v>
@@ -980,21 +1365,33 @@
         <v>60</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S24" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="T24" t="s">
+        <v>89</v>
+      </c>
+      <c r="U24" t="s">
+        <v>29</v>
+      </c>
+      <c r="V24" t="s">
+        <v>90</v>
+      </c>
+      <c r="W24" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="D25">
         <v>32</v>
@@ -1003,21 +1400,33 @@
         <v>50</v>
       </c>
       <c r="R25" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="S25" t="s">
+        <v>41</v>
+      </c>
+      <c r="T25" t="s">
+        <v>133</v>
+      </c>
+      <c r="U25" t="s">
+        <v>29</v>
+      </c>
+      <c r="V25" t="s">
+        <v>134</v>
+      </c>
+      <c r="W25" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="D26">
         <v>8.9</v>
@@ -1026,10 +1435,22 @@
         <v>40</v>
       </c>
       <c r="R26" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="T26" t="s">
+        <v>137</v>
+      </c>
+      <c r="U26" t="s">
+        <v>29</v>
+      </c>
+      <c r="V26" t="s">
+        <v>138</v>
+      </c>
+      <c r="W26" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
